--- a/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/feb-2025.xlsx
+++ b/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/feb-2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC feb-2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC feb-2025" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,7 +549,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">

--- a/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/feb-2025.xlsx
+++ b/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/feb-2025.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -562,7 +562,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -697,7 +709,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>609685-3-CM25</t>
+          <t>593951-35-SE25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -712,22 +724,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-02-12</t>
+          <t>2025-02-06</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>53.314.782-8</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>DIRECCION DE COMPRAS Y CONTRATACION PUBLICA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -745,20 +757,24 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>46247.11</v>
+        <v>4811254.64</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>931071-1-CM25</t>
+          <t>609685-3-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -773,7 +789,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2025-02-12</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -783,12 +799,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>61.980.750-2</t>
+          <t>53.314.782-8</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>UNIDAD DE ANALISIS FINANCIERO</t>
+          <t>DIRECCION DE COMPRAS Y CONTRATACION PUBLICA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -806,20 +822,24 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>37192.52</v>
+        <v>46247.11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>543511-3-CM25</t>
+          <t>931071-1-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -834,22 +854,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-02-14</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>61.706.000-0</t>
+          <t>61.980.750-2</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Comisión Chilena del Cobre - COCHILCO</t>
+          <t>UNIDAD DE ANALISIS FINANCIERO</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -867,20 +887,24 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>38249.29</v>
+        <v>37192.52</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2701-124-CM25</t>
+          <t>543511-3-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -895,22 +919,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-02-18</t>
+          <t>2025-02-14</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>69.071.800-6</t>
+          <t>61.706.000-0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+          <t>Comisión Chilena del Cobre - COCHILCO</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -928,20 +952,24 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>6690.04</v>
+        <v>38249.29</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1273563-1-CM25</t>
+          <t>2701-124-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -966,12 +994,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>62.000.740-4</t>
+          <t>69.071.800-6</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE CIENCIA, TECNOLOGIA, CONOCIMIENTO E INNOVACION</t>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -989,20 +1017,24 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>36836.51</v>
+        <v>6690.04</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1076575-1-CM25</t>
+          <t>1273563-1-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1017,7 +1049,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-02-19</t>
+          <t>2025-02-18</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1027,17 +1059,17 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>60.110.000-2</t>
+          <t>62.000.740-4</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE LA JUVENTUD</t>
+          <t>SUBSECRETARIA DE CIENCIA, TECNOLOGIA, CONOCIMIENTO E INNOVACION</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1050,20 +1082,24 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>52696.62</v>
+        <v>36836.51</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>561201-3-CM25</t>
+          <t>1076575-1-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1088,17 +1124,17 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>61.701.000-3</t>
+          <t>60.110.000-2</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE MINERIA</t>
+          <t>INSTITUTO NACIONAL DE LA JUVENTUD</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1111,20 +1147,24 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>42980.68</v>
+        <v>52696.62</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>606591-2-CM25</t>
+          <t>561201-3-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1139,22 +1179,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025-02-21</t>
+          <t>2025-02-19</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>60.718.000-8</t>
+          <t>61.701.000-3</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>COMISION NACIONAL DE RIEGO</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE MINERIA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1172,20 +1212,24 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>69641.89999999999</v>
+        <v>42980.68</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>606591-3-CM25</t>
+          <t>606591-2-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,7 +1249,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1233,20 +1277,24 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>4974.42</v>
+        <v>69641.89999999999</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>670784-2-CM25</t>
+          <t>606591-3-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1261,22 +1309,22 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>2025-02-21</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>60.818.000-1</t>
+          <t>60.718.000-8</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>SUPERINTENDENCIA DE PENSIONES</t>
+          <t>COMISION NACIONAL DE RIEGO</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1294,20 +1342,24 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>8527.16</v>
+        <v>4974.42</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>550716-2-CM25</t>
+          <t>670784-2-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1332,12 +1384,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>65.961.370-0</t>
+          <t>60.818.000-1</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
+          <t>SUPERINTENDENCIA DE PENSIONES</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1355,20 +1407,24 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>5906.62</v>
+        <v>8527.16</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>603663-31-CM25</t>
+          <t>550716-2-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1383,22 +1439,22 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>65.028.707-K</t>
+          <t>65.961.370-0</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DERECHOS HUMANOS</t>
+          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1416,20 +1472,24 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>69580.67999999999</v>
+        <v>5906.62</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1221275-2-CM25</t>
+          <t>603663-31-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1444,22 +1504,22 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>60.108.000-1</t>
+          <t>65.028.707-K</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>AGENCIA CHILENA DE COOPERACION INTERNACIONAL PARA EL DESARROLLO</t>
+          <t>INSTITUTO NACIONAL DE DERECHOS HUMANOS</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1477,20 +1537,24 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>38026.86</v>
+        <v>69580.67999999999</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1186801-2-CM25</t>
+          <t>1221275-2-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1505,22 +1569,22 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>60.930.000-0</t>
+          <t>60.108.000-1</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>CONSEJO NACIONAL DE EDUCACION</t>
+          <t>AGENCIA CHILENA DE COOPERACION INTERNACIONAL PARA EL DESARROLLO</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1538,20 +1602,24 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>1060.83</v>
+        <v>38026.86</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>544143-2-CM25</t>
+          <t>1186801-2-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1566,7 +1634,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1576,17 +1644,17 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>60.701.002-1</t>
+          <t>60.930.000-0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>SERV NACIONAL DE PESCA</t>
+          <t>CONSEJO NACIONAL DE EDUCACION</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1599,20 +1667,24 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>31876.29</v>
+        <v>1060.83</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2595-72-CM25</t>
+          <t>544143-2-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1637,17 +1709,17 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>69.130.700-K</t>
+          <t>60.701.002-1</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PARRAL</t>
+          <t>SERV NACIONAL DE PESCA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1660,74 +1732,147 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>10072.41</v>
+        <v>31876.29</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>2595-72-CM25</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>feb-2025</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>69.130.700-K</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PARRAL</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="n">
+        <v>10072.41</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>1076575-2-CM25</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2239-12-LR23</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>feb-2025</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>feb-2025</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
         <is>
           <t>2025-02-28</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>Aceptada</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>60.110.000-2</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>INSTITUTO NACIONAL DE LA JUVENTUD</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>O'Higgins</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>BCI SEGUROS VIDA S A</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>96.573.600-K</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="n">
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="n">
         <v>22882.98</v>
       </c>
     </row>
